--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:17</t>
+    <t xml:space="preserve">2026-09-29 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:07</t>
+    <t xml:space="preserve">2026-09-29 18:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -518,7 +518,7 @@
         <v>1.81</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>37.18</v>
+        <v>37.19</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>35.38</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:44</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
